--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486667_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486667_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8222</v>
+        <v>8.4594</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7843</v>
+        <v>8.198</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0379</v>
+        <v>0.2614</v>
       </c>
       <c r="G2" t="n">
         <v>6.2249</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3681</v>
+        <v>-0.7309</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5518</v>
+        <v>-0.1381</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8163</v>
+        <v>-0.5928</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4266</v>
+        <v>6.348</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4132</v>
+        <v>5.3098</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0134</v>
+        <v>1.0383</v>
       </c>
       <c r="G3" t="n">
         <v>3.8568</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5074</v>
+        <v>-0.586</v>
       </c>
       <c r="T3" t="n">
-        <v>0.165</v>
+        <v>0.0615</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6723</v>
+        <v>-0.6475</v>
       </c>
       <c r="V3" t="n">
         <v>2.498</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>A. OMERAGIC ALIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.29</v>
+        <v>1.1071</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9094</v>
+        <v>-1.2229</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3806</v>
+        <v>2.33</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2141</v>
+        <v>-0.7951</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6904</v>
+        <v>-0.4696</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5236</v>
+        <v>-0.3255</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2089</v>
+        <v>-1.4904</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1742</v>
+        <v>-0.1929</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0346</v>
+        <v>-1.2976</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9948</v>
+        <v>0.6953</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4838</v>
+        <v>-0.2767</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.511</v>
+        <v>0.972</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3169</v>
+        <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2191</v>
+        <v>-0.6617</v>
       </c>
       <c r="T4" t="n">
-        <v>1.875</v>
+        <v>-0.3037</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6559</v>
+        <v>-0.358</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5985</v>
+        <v>1.5985</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.3129</v>
+        <v>0.5712</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>1.0273</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. OMERAGIC ALIC</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6366</v>
+        <v>-0.3317</v>
       </c>
       <c r="F5" t="n">
-        <v>2.628</v>
+        <v>0.4303</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7951</v>
+        <v>3.2141</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4696</v>
+        <v>1.6904</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3255</v>
+        <v>1.5236</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4904</v>
+        <v>4.2089</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1929</v>
+        <v>2.1742</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2976</v>
+        <v>2.0346</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6953</v>
+        <v>-0.9948</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2767</v>
+        <v>-0.4838</v>
       </c>
       <c r="O5" t="n">
-        <v>0.972</v>
+        <v>-0.511</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9654</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9654</v>
+        <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7774</v>
+        <v>0.0277</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7174</v>
+        <v>0.6339</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06</v>
+        <v>-0.6062</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5985</v>
+        <v>-1.5985</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5712</v>
+        <v>-1.3129</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0273</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7862</v>
+        <v>-0.697</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9102</v>
+        <v>-1.1138</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1241</v>
+        <v>0.4168</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6206</v>
+        <v>0.3371</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7585</v>
+        <v>-1.7178</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1379</v>
+        <v>2.0549</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6895</v>
+        <v>1.2143</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6895</v>
+        <v>-0.1308</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.3451</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0689</v>
+        <v>-0.8772</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-1.587</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1379</v>
+        <v>0.7098</v>
       </c>
       <c r="P6" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1931</v>
+        <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3586</v>
+        <v>-1.8411</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2207</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1379</v>
+        <v>-1.1581</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0569</v>
+        <v>-0.7862</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4241</v>
+        <v>-0.9102</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3672</v>
+        <v>0.1241</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3371</v>
+        <v>-0.6206</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7178</v>
+        <v>-0.7585</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0549</v>
+        <v>0.1379</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2143</v>
+        <v>-0.6895</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1308</v>
+        <v>-0.6895</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3451</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8772</v>
+        <v>0.0689</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.587</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7098</v>
+        <v>0.1379</v>
       </c>
       <c r="P7" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1239</v>
+        <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.201</v>
+        <v>-0.3586</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9933</v>
+        <v>-0.2207</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2077</v>
+        <v>-0.1379</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6552</v>
+        <v>-1.2248</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0589</v>
+        <v>-1.852</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4037</v>
+        <v>0.6272</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8386</v>
@@ -1078,13 +1078,13 @@
         <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2027</v>
+        <v>-0.7723</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6622</v>
+        <v>-0.4553</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5405</v>
+        <v>-0.317</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRIGUEZ</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.771</v>
+        <v>-2.0727</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9446</v>
+        <v>-0.9406</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1736</v>
+        <v>-1.1321</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2689</v>
+        <v>-2.8725</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9931</v>
+        <v>-1.9659</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2758</v>
+        <v>-0.9066</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3376</v>
+        <v>-0.9058</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6481</v>
+        <v>-0.3791</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6895</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0687</v>
+        <v>-1.9667</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.345</v>
+        <v>-1.5868</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4137</v>
+        <v>-0.3799</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7377</v>
+        <v>1.7377</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2355</v>
+        <v>-0.3241</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3238</v>
+        <v>-0.0348</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0882</v>
+        <v>-0.2892</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0023</v>
+        <v>-2.2026</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0441</v>
+        <v>-1.1604</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.0422</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8725</v>
+        <v>-0.6785</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9659</v>
+        <v>-0.5451</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9066</v>
+        <v>-0.1334</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9058</v>
+        <v>-0.4913</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3791</v>
+        <v>0.0761</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5674</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9667</v>
+        <v>-0.1872</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5868</v>
+        <v>-0.6212</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3799</v>
+        <v>0.434</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2537</v>
+        <v>-1.0687</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1383</v>
+        <v>-0.6691</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1154</v>
+        <v>-0.3996</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6138</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6138</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>G. CAMPOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2315</v>
+        <v>-2.5239</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2638</v>
+        <v>-2.772</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9677</v>
+        <v>0.2481</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6785</v>
+        <v>-1.2689</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5451</v>
+        <v>-0.9931</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1334</v>
+        <v>-0.2758</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4913</v>
+        <v>-1.3376</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0761</v>
+        <v>-0.6481</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5674</v>
+        <v>-0.6895</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1872</v>
+        <v>0.0687</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6212</v>
+        <v>-0.345</v>
       </c>
       <c r="O11" t="n">
-        <v>0.434</v>
+        <v>0.4137</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7723</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0976</v>
+        <v>0.4827</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7725</v>
+        <v>0.4964</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3251</v>
+        <v>-0.0137</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5992</v>
+        <v>-3.078</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6496</v>
+        <v>-3.0291</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0505</v>
+        <v>-0.0488</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6977</v>
@@ -1390,13 +1390,13 @@
         <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.5931</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2759</v>
+        <v>0.3446</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3478</v>
+        <v>0.2485</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6565</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.427900000000001</v>
+        <v>3.427900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1750000000000003</v>
+        <v>0.1750999999999987</v>
       </c>
       <c r="F13" t="n">
         <v>3.2531</v>
@@ -1459,7 +1459,7 @@
         <v>1.5819</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9655</v>
+        <v>0.9654999999999991</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.5502</v>
@@ -1468,13 +1468,13 @@
         <v>13.5155</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.24</v>
+        <v>-5.2399</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9682999999999997</v>
+        <v>-0.9683000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.2715</v>
+        <v>-4.271500000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.8415</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. ELTING</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1849</v>
+        <v>2.214</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8272</v>
+        <v>-0.4873</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3577</v>
+        <v>2.7013</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0472</v>
+        <v>-0.71</v>
       </c>
       <c r="H14" t="n">
-        <v>2.91</v>
+        <v>-1.5374</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8628</v>
+        <v>0.8274</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0206</v>
+        <v>-1.3302</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3589</v>
+        <v>-1.3302</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3383</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0266</v>
+        <v>0.6201</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5511</v>
+        <v>-0.2072</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5245</v>
+        <v>0.8274</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9599</v>
+        <v>0.1171</v>
       </c>
       <c r="T14" t="n">
-        <v>0.772</v>
+        <v>0.3376</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1879</v>
+        <v>-0.2205</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3709</v>
+        <v>1.8415</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="X14" t="n">
         <v>0.3709</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>B. ELTING</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8605</v>
+        <v>2.0525</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7032</v>
+        <v>0.6204</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8427</v>
+        <v>1.4322</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6856</v>
+        <v>1.0472</v>
       </c>
       <c r="H15" t="n">
-        <v>0.076</v>
+        <v>2.91</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6096</v>
+        <v>-1.8628</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6249</v>
+        <v>1.0206</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6287</v>
+        <v>2.3589</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9962</v>
+        <v>-1.3383</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.9393</v>
+        <v>0.0266</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.5527</v>
+        <v>0.5511</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3866</v>
+        <v>-0.5245</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3169</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5498</v>
+        <v>0.8275</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6543</v>
+        <v>0.5651</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1044</v>
+        <v>0.2624</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9421</v>
+        <v>0.3709</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6565</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7051</v>
+        <v>1.3931</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7976</v>
+        <v>2.1861</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5026</v>
+        <v>-0.793</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.71</v>
+        <v>1.6856</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5374</v>
+        <v>0.076</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8274</v>
+        <v>1.6096</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3302</v>
+        <v>4.6249</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3302</v>
+        <v>2.6287</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.9962</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6201</v>
+        <v>-2.9393</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2072</v>
+        <v>-2.5527</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8274</v>
+        <v>-0.3866</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9654</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3919</v>
+        <v>1.0824</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0273</v>
+        <v>1.1372</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4191</v>
+        <v>-0.0548</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8415</v>
+        <v>0.9421</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4707</v>
+        <v>0.2856</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3709</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9319</v>
+        <v>1.2381</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.993</v>
+        <v>-0.7861</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9249</v>
+        <v>2.0242</v>
       </c>
       <c r="G17" t="n">
         <v>0.5721000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3199</v>
+        <v>-0.0138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3863</v>
+        <v>-0.1794</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0663</v>
+        <v>0.1657</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2828</v>
+        <v>0.3862</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2477</v>
+        <v>-1.1443</v>
       </c>
       <c r="F18" t="n">
         <v>1.5304</v>
@@ -1858,10 +1858,10 @@
         <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6344</v>
+        <v>0.7378</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3584</v>
+        <v>0.4618</v>
       </c>
       <c r="U18" t="n">
         <v>0.276</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3434</v>
+        <v>-0.5342</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1418</v>
+        <v>1.9527</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4852</v>
+        <v>-2.487</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0793</v>
+        <v>1.9473</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6135</v>
+        <v>1.6897</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4657</v>
+        <v>0.2577</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8229</v>
+        <v>4.673</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0264</v>
+        <v>3.8976</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2035</v>
+        <v>0.7754</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2563</v>
+        <v>-2.7257</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5871</v>
+        <v>-2.2079</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6692</v>
+        <v>-0.5178</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1567</v>
+        <v>0.7308</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9302</v>
+        <v>0.5235</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2265</v>
+        <v>0.2073</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.8262</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-1.3129</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8238</v>
+        <v>-1.5555</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5391</v>
+        <v>-0.9958</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3628</v>
+        <v>-0.5597</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9473</v>
+        <v>-3.0793</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6897</v>
+        <v>-2.6135</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2577</v>
+        <v>-0.4657</v>
       </c>
       <c r="J20" t="n">
-        <v>4.673</v>
+        <v>-0.8229</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8976</v>
+        <v>-1.0264</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7754</v>
+        <v>0.2035</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7257</v>
+        <v>-2.2563</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2079</v>
+        <v>-1.5871</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5178</v>
+        <v>-0.6692</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4413</v>
+        <v>0.9445</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1098</v>
+        <v>0.7925</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3315</v>
+        <v>0.152</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.8262</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.3129</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6262</v>
+        <v>-2.3697</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0923</v>
+        <v>-0.8855</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5339</v>
+        <v>-1.4842</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0649</v>
@@ -2092,13 +2092,13 @@
         <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3256</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0546</v>
+        <v>0.2614</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3802</v>
+        <v>-0.3306</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6565</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5998</v>
+        <v>-6.2524</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3338</v>
+        <v>-3.7132</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.266</v>
+        <v>-2.5392</v>
       </c>
       <c r="G22" t="n">
         <v>-5.9074</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5353</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2486</v>
+        <v>0.3719</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7839</v>
+        <v>0.5107</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.428</v>
+        <v>-3.427899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.253100000000001</v>
+        <v>-3.253</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1750000000000003</v>
+        <v>-0.1750000000000007</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8611</v>
@@ -2218,7 +2218,7 @@
         <v>-0.3451</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.515699999999999</v>
+        <v>-5.5157</v>
       </c>
       <c r="J23" t="n">
         <v>4.9763</v>
@@ -2239,7 +2239,7 @@
         <v>-3.9339</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9653999999999997</v>
+        <v>-0.9653999999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.5156</v>
@@ -2248,13 +2248,13 @@
         <v>12.55</v>
       </c>
       <c r="S23" t="n">
-        <v>5.24</v>
+        <v>5.2398</v>
       </c>
       <c r="T23" t="n">
-        <v>4.271700000000001</v>
+        <v>4.2716</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9684000000000001</v>
+        <v>0.9682000000000002</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8415</v>
